--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487180_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487180_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.56</v>
+        <v>7.8188</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4438</v>
+        <v>6.3451</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1162</v>
+        <v>1.4737</v>
       </c>
       <c r="G2" t="n">
         <v>3.4171</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5639</v>
+        <v>1.8227</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0582</v>
+        <v>0.9594</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5057</v>
+        <v>0.8632</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2327</v>
+        <v>7.6744</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4176</v>
+        <v>6.779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8151</v>
+        <v>0.8954</v>
       </c>
       <c r="G3" t="n">
         <v>3.3361</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4105</v>
+        <v>1.8521</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0132</v>
+        <v>1.3746</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3972</v>
+        <v>0.4775</v>
       </c>
       <c r="V3" t="n">
         <v>0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.0846</v>
+        <v>5.8644</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2779</v>
+        <v>6.7366</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1933</v>
+        <v>-0.8721</v>
       </c>
       <c r="G4" t="n">
         <v>3.5411</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7715</v>
+        <v>1.5513</v>
       </c>
       <c r="T4" t="n">
-        <v>1.675</v>
+        <v>1.1336</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0965</v>
+        <v>0.4177</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.912</v>
+        <v>5.452</v>
       </c>
       <c r="E5" t="n">
-        <v>4.665</v>
+        <v>3.964</v>
       </c>
       <c r="F5" t="n">
-        <v>1.247</v>
+        <v>1.4879</v>
       </c>
       <c r="G5" t="n">
         <v>1.1546</v>
@@ -844,13 +844,13 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8805</v>
+        <v>1.4205</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7636</v>
+        <v>1.0626</v>
       </c>
       <c r="U5" t="n">
-        <v>0.117</v>
+        <v>0.3579</v>
       </c>
       <c r="V5" t="n">
         <v>3.0699</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0834</v>
+        <v>4.0636</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3368</v>
+        <v>2.9958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7466</v>
+        <v>1.0678</v>
       </c>
       <c r="G6" t="n">
         <v>0.8985</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5481</v>
+        <v>1.5282</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6591</v>
+        <v>1.318</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1111</v>
+        <v>0.2102</v>
       </c>
       <c r="V6" t="n">
         <v>0.2859</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5981</v>
+        <v>3.03</v>
       </c>
       <c r="E7" t="n">
-        <v>1.513</v>
+        <v>1.2126</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0852</v>
+        <v>1.8175</v>
       </c>
       <c r="G7" t="n">
         <v>1.7305</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3815</v>
+        <v>0.8133</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5037</v>
+        <v>0.2033</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8778</v>
+        <v>0.6101</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2666</v>
+        <v>2.1774</v>
       </c>
       <c r="E8" t="n">
-        <v>1.755</v>
+        <v>0.6241</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5117</v>
+        <v>1.5533</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2751</v>
+        <v>-1.1578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1708</v>
+        <v>-2.955</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1042</v>
+        <v>1.7972</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9218</v>
+        <v>-1.3181</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1242</v>
+        <v>-2.5876</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7976</v>
+        <v>1.2695</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0466</v>
+        <v>-0.3674</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6933</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1846</v>
+        <v>1.0421</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7054</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4792</v>
+        <v>0.3278</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2859</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7699</v>
+        <v>1.3921</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3237</v>
+        <v>0.8537</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4462</v>
+        <v>0.5384</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1578</v>
+        <v>0.2751</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.955</v>
+        <v>0.1708</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7972</v>
+        <v>0.1042</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3181</v>
+        <v>0.9218</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5876</v>
+        <v>0.1242</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2695</v>
+        <v>0.7976</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1603</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3674</v>
+        <v>0.0466</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.6933</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.3101</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4138</v>
+        <v>0.8041</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2208</v>
+        <v>0.506</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2859</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ MARCILLA</t>
+          <t>A. RUIZ VICENTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3312</v>
+        <v>0.1919</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2684</v>
+        <v>-0.1285</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4189</v>
+        <v>-0.7981</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6924</v>
+        <v>0.1201</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2735</v>
+        <v>-0.9182</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9729</v>
+        <v>0.5763</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9729</v>
+        <v>1.1953</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.619</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-1.3744</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2805</v>
+        <v>-1.0752</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2735</v>
+        <v>-0.2992</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1071</v>
+        <v>0.8616</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0145</v>
+        <v>0.2948</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0925</v>
+        <v>0.5668</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>D. FERNANDEZ MARCILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0485</v>
+        <v>-0.0443</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1125</v>
+        <v>0.3312</v>
       </c>
       <c r="F11" t="n">
-        <v>0.161</v>
+        <v>-0.3755</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.37</v>
+        <v>0.4189</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2629</v>
+        <v>0.6924</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.633</v>
+        <v>-0.2735</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.763</v>
+        <v>0.9729</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1178</v>
+        <v>0.9729</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8807</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6071</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8548</v>
+        <v>-0.2805</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2478</v>
+        <v>-0.2735</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1905</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6155</v>
+        <v>0.0145</v>
       </c>
       <c r="U11" t="n">
-        <v>0.575</v>
+        <v>-0.0145</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ VICENTE</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6098</v>
+        <v>-0.8468</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6687</v>
+        <v>-0.9543</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0589</v>
+        <v>0.1074</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7981</v>
+        <v>-1.37</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1201</v>
+        <v>0.2629</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9182</v>
+        <v>-1.633</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5763</v>
+        <v>-0.763</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1953</v>
+        <v>1.1178</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.619</v>
+        <v>-1.8807</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3744</v>
+        <v>-0.6071</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0752</v>
+        <v>-0.8548</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2992</v>
+        <v>0.2478</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-0.772</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>0.965</v>
+        <v>0.193</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1884</v>
+        <v>1.2952</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5658</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7542</v>
+        <v>0.5215</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.221</v>
+        <v>-3.5597</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3719</v>
+        <v>-2.8712</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8492</v>
+        <v>-0.6886</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4371</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2049</v>
+        <v>0.4564</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0449</v>
+        <v>0.4558</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.16</v>
+        <v>0.0007</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.7878</v>
+        <v>33.0854</v>
       </c>
       <c r="E14" t="n">
-        <v>25.91089999999999</v>
+        <v>26.2085</v>
       </c>
       <c r="F14" t="n">
-        <v>6.877000000000001</v>
+        <v>6.8767</v>
       </c>
       <c r="G14" t="n">
         <v>10.0089</v>
@@ -1516,7 +1516,7 @@
         <v>2.5043</v>
       </c>
       <c r="I14" t="n">
-        <v>7.504300000000002</v>
+        <v>7.5043</v>
       </c>
       <c r="J14" t="n">
         <v>15.409</v>
@@ -1525,7 +1525,7 @@
         <v>7.647399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.761700000000001</v>
+        <v>7.7617</v>
       </c>
       <c r="M14" t="n">
         <v>-5.4002</v>
@@ -1546,13 +1546,13 @@
         <v>12.5455</v>
       </c>
       <c r="S14" t="n">
-        <v>13.6563</v>
+        <v>13.9535</v>
       </c>
       <c r="T14" t="n">
-        <v>8.811300000000001</v>
+        <v>9.108600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>4.844799999999999</v>
+        <v>4.8449</v>
       </c>
       <c r="V14" t="n">
         <v>4.2979</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3955</v>
+        <v>-0.2154</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1559</v>
+        <v>-0.0557</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2397</v>
+        <v>-0.1597</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2118</v>
@@ -1624,13 +1624,13 @@
         <v>0.193</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3768</v>
+        <v>-0.1966</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1388</v>
+        <v>-0.0588</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.3829</v>
+        <v>-1.7553</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.7417</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.441</v>
+        <v>-1.0136</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3081</v>
@@ -1702,13 +1702,13 @@
         <v>0.386</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3028</v>
+        <v>-0.6752</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2829</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0199</v>
+        <v>-0.5926</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9127</v>
+        <v>-1.9847</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9425</v>
+        <v>-0.4418</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9703</v>
+        <v>-1.5429</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2718</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3128</v>
+        <v>-1.3848</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4132</v>
+        <v>-0.9125</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8996</v>
+        <v>-0.4723</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4526</v>
+        <v>-2.6912</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6845</v>
+        <v>-1.4842</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7681</v>
+        <v>-1.207</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8226</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.823</v>
+        <v>-1.0615</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5949</v>
+        <v>-0.3946</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2281</v>
+        <v>-0.6669</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5919</v>
+        <v>-3.1101</v>
       </c>
       <c r="E19" t="n">
-        <v>0.746</v>
+        <v>0.3454</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.3379</v>
+        <v>-3.4555</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1172</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.166</v>
+        <v>-0.6841</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.078</v>
+        <v>-0.4785</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.088</v>
+        <v>-0.2056</v>
       </c>
       <c r="V19" t="n">
         <v>0.6562</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. VILLAVERDE GONZALEZ</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6392</v>
+        <v>-3.969</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6421</v>
+        <v>0.5793</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.2813</v>
+        <v>-4.5483</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3402</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.353</v>
+        <v>1.0329</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0129</v>
+        <v>-1.7058</v>
       </c>
       <c r="J20" t="n">
-        <v>1.714</v>
+        <v>1.7745</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0143</v>
+        <v>1.6609</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6998</v>
+        <v>0.1135</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3739</v>
+        <v>-2.4474</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6612</v>
+        <v>-0.628</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7126</v>
+        <v>-1.8194</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3161</v>
+        <v>-0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0881</v>
+        <v>-2.1231</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1495</v>
+        <v>-1.4469</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5024</v>
+        <v>-0.8718</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.6518</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5138</v>
+        <v>-1.2702</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5138</v>
+        <v>1.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0277</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8349</v>
+        <v>-4.3874</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0239</v>
+        <v>-2.3243</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.811</v>
+        <v>-2.0631</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3632</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3366</v>
+        <v>-1.8891</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6411</v>
+        <v>-0.9415</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6955</v>
+        <v>-0.9476</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>I. VILLAVERDE GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9427</v>
+        <v>-4.9595</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0215</v>
+        <v>-0.159</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9212</v>
+        <v>-4.8005</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.3402</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0329</v>
+        <v>0.353</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7058</v>
+        <v>-0.0129</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7745</v>
+        <v>1.714</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6609</v>
+        <v>1.0143</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1135</v>
+        <v>0.6998</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4474</v>
+        <v>-1.3739</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.628</v>
+        <v>-0.6612</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8194</v>
+        <v>-0.7126</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.579</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1231</v>
+        <v>-3.0881</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.4206</v>
+        <v>-1.4697</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4726</v>
+        <v>-0.2987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9479</v>
+        <v>-1.171</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2702</v>
+        <v>-1.5138</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>1.5138</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.0699</v>
+        <v>-3.0277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6353</v>
+        <v>-5.7096</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4948</v>
+        <v>-2.5949</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1405</v>
+        <v>-3.1147</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5813</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7681</v>
+        <v>-0.8424</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6266</v>
+        <v>-0.7267</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1415</v>
+        <v>-0.1157</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.78769999999999</v>
+        <v>-28.7822</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.876999999999999</v>
+        <v>-6.8769</v>
       </c>
       <c r="F24" t="n">
-        <v>-25.911</v>
+        <v>-21.9053</v>
       </c>
       <c r="G24" t="n">
         <v>-10.0087</v>
@@ -2311,13 +2311,13 @@
         <v>-15.409</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.647200000000001</v>
+        <v>-7.6472</v>
       </c>
       <c r="O24" t="n">
         <v>-7.7615</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.8251</v>
+        <v>-4.825100000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.5454</v>
@@ -2326,19 +2326,19 @@
         <v>7.7203</v>
       </c>
       <c r="S24" t="n">
-        <v>-13.6562</v>
+        <v>-9.6503</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.844899999999999</v>
+        <v>-4.8447</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.8111</v>
+        <v>-4.8056</v>
       </c>
       <c r="V24" t="n">
         <v>-4.297800000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>5.1133</v>
+        <v>5.113300000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-9.411099999999999</v>
